--- a/data/full-survey-results.xlsx
+++ b/data/full-survey-results.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DV2"/>
+  <dimension ref="A1:EL11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -593,210 +593,258 @@
         <v>s3_base_price_brl</v>
       </c>
       <c r="BM1" t="str">
-        <v>s3_session_1_weight</v>
+        <v>s3_randomization_seed</v>
       </c>
       <c r="BN1" t="str">
-        <v>s3_session_2_weight</v>
+        <v>s3_top_seal_1</v>
       </c>
       <c r="BO1" t="str">
-        <v>s3_randomization_seed</v>
+        <v>s3_top_seal_2</v>
       </c>
       <c r="BP1" t="str">
-        <v>s3_top_seal_1</v>
+        <v>s3_top_seal_3</v>
       </c>
       <c r="BQ1" t="str">
-        <v>s3_top_seal_2</v>
+        <v>s3_rank_1_option_id</v>
       </c>
       <c r="BR1" t="str">
-        <v>s3_top_seal_3</v>
+        <v>s3_rank_1_cut_id</v>
       </c>
       <c r="BS1" t="str">
-        <v>s3_round_1_rank_1_option_id</v>
+        <v>s3_rank_1_seal_id</v>
       </c>
       <c r="BT1" t="str">
-        <v>s3_round_1_rank_1_cut_id</v>
+        <v>s3_rank_1_title</v>
       </c>
       <c r="BU1" t="str">
-        <v>s3_round_1_rank_1_seal_id</v>
+        <v>s3_rank_1_price_brl</v>
       </c>
       <c r="BV1" t="str">
-        <v>s3_round_1_rank_1_title</v>
+        <v>s3_rank_1_price_increase_percent</v>
       </c>
       <c r="BW1" t="str">
-        <v>s3_round_1_rank_1_price_brl</v>
+        <v>s3_rank_2_option_id</v>
       </c>
       <c r="BX1" t="str">
-        <v>s3_round_1_rank_1_price_increase_percent</v>
+        <v>s3_rank_2_cut_id</v>
       </c>
       <c r="BY1" t="str">
-        <v>s3_round_1_rank_2_option_id</v>
+        <v>s3_rank_2_seal_id</v>
       </c>
       <c r="BZ1" t="str">
-        <v>s3_round_1_rank_2_cut_id</v>
+        <v>s3_rank_2_title</v>
       </c>
       <c r="CA1" t="str">
-        <v>s3_round_1_rank_2_seal_id</v>
+        <v>s3_rank_2_price_brl</v>
       </c>
       <c r="CB1" t="str">
-        <v>s3_round_1_rank_2_title</v>
+        <v>s3_rank_2_price_increase_percent</v>
       </c>
       <c r="CC1" t="str">
-        <v>s3_round_1_rank_2_price_brl</v>
+        <v>s3_rank_3_option_id</v>
       </c>
       <c r="CD1" t="str">
-        <v>s3_round_1_rank_2_price_increase_percent</v>
+        <v>s3_rank_3_cut_id</v>
       </c>
       <c r="CE1" t="str">
-        <v>s3_round_1_rank_3_option_id</v>
+        <v>s3_rank_3_seal_id</v>
       </c>
       <c r="CF1" t="str">
-        <v>s3_round_1_rank_3_cut_id</v>
+        <v>s3_rank_3_title</v>
       </c>
       <c r="CG1" t="str">
-        <v>s3_round_1_rank_3_seal_id</v>
+        <v>s3_rank_3_price_brl</v>
       </c>
       <c r="CH1" t="str">
-        <v>s3_round_1_rank_3_title</v>
+        <v>s3_rank_3_price_increase_percent</v>
       </c>
       <c r="CI1" t="str">
-        <v>s3_round_1_rank_3_price_brl</v>
+        <v>s3_timestamp</v>
       </c>
       <c r="CJ1" t="str">
-        <v>s3_round_1_rank_3_price_increase_percent</v>
+        <v>full_survey_saved_at</v>
       </c>
       <c r="CK1" t="str">
-        <v>s3_round_2_rank_1_option_id</v>
+        <v>s3_screen_1_rank_1_option_id</v>
       </c>
       <c r="CL1" t="str">
-        <v>s3_round_2_rank_1_cut_id</v>
+        <v>s3_screen_1_rank_1_seal_id</v>
       </c>
       <c r="CM1" t="str">
-        <v>s3_round_2_rank_1_seal_id</v>
+        <v>s3_screen_1_rank_1_title</v>
       </c>
       <c r="CN1" t="str">
-        <v>s3_round_2_rank_1_title</v>
+        <v>s3_screen_1_rank_1_subtitle</v>
       </c>
       <c r="CO1" t="str">
-        <v>s3_round_2_rank_1_price_brl</v>
+        <v>s3_screen_1_rank_1_price_brl</v>
       </c>
       <c r="CP1" t="str">
-        <v>s3_round_2_rank_1_price_increase_percent</v>
+        <v>s3_screen_1_rank_1_price_increase_percent</v>
       </c>
       <c r="CQ1" t="str">
-        <v>s3_round_2_rank_2_option_id</v>
+        <v>s3_screen_1_rank_2_option_id</v>
       </c>
       <c r="CR1" t="str">
-        <v>s3_round_2_rank_2_cut_id</v>
+        <v>s3_screen_1_rank_2_seal_id</v>
       </c>
       <c r="CS1" t="str">
-        <v>s3_round_2_rank_2_seal_id</v>
+        <v>s3_screen_1_rank_2_title</v>
       </c>
       <c r="CT1" t="str">
-        <v>s3_round_2_rank_2_title</v>
+        <v>s3_screen_1_rank_2_subtitle</v>
       </c>
       <c r="CU1" t="str">
-        <v>s3_round_2_rank_2_price_brl</v>
+        <v>s3_screen_1_rank_2_price_brl</v>
       </c>
       <c r="CV1" t="str">
-        <v>s3_round_2_rank_2_price_increase_percent</v>
+        <v>s3_screen_1_rank_2_price_increase_percent</v>
       </c>
       <c r="CW1" t="str">
-        <v>s3_round_2_rank_3_option_id</v>
+        <v>s3_screen_1_rank_3_option_id</v>
       </c>
       <c r="CX1" t="str">
-        <v>s3_round_2_rank_3_cut_id</v>
+        <v>s3_screen_1_rank_3_seal_id</v>
       </c>
       <c r="CY1" t="str">
-        <v>s3_round_2_rank_3_seal_id</v>
+        <v>s3_screen_1_rank_3_title</v>
       </c>
       <c r="CZ1" t="str">
-        <v>s3_round_2_rank_3_title</v>
+        <v>s3_screen_1_rank_3_subtitle</v>
       </c>
       <c r="DA1" t="str">
-        <v>s3_round_2_rank_3_price_brl</v>
+        <v>s3_screen_1_rank_3_price_brl</v>
       </c>
       <c r="DB1" t="str">
-        <v>s3_round_2_rank_3_price_increase_percent</v>
+        <v>s3_screen_1_rank_3_price_increase_percent</v>
       </c>
       <c r="DC1" t="str">
-        <v>s3_round_3_rank_1_option_id</v>
+        <v>s3_screen_2_rank_1_option_id</v>
       </c>
       <c r="DD1" t="str">
-        <v>s3_round_3_rank_1_cut_id</v>
+        <v>s3_screen_2_rank_1_seal_id</v>
       </c>
       <c r="DE1" t="str">
-        <v>s3_round_3_rank_1_seal_id</v>
+        <v>s3_screen_2_rank_1_title</v>
       </c>
       <c r="DF1" t="str">
-        <v>s3_round_3_rank_1_title</v>
+        <v>s3_screen_2_rank_1_subtitle</v>
       </c>
       <c r="DG1" t="str">
-        <v>s3_round_3_rank_1_price_brl</v>
+        <v>s3_screen_2_rank_1_price_brl</v>
       </c>
       <c r="DH1" t="str">
-        <v>s3_round_3_rank_1_price_increase_percent</v>
+        <v>s3_screen_2_rank_1_price_increase_percent</v>
       </c>
       <c r="DI1" t="str">
-        <v>s3_round_3_rank_2_option_id</v>
+        <v>s3_screen_2_rank_2_option_id</v>
       </c>
       <c r="DJ1" t="str">
-        <v>s3_round_3_rank_2_cut_id</v>
+        <v>s3_screen_2_rank_2_seal_id</v>
       </c>
       <c r="DK1" t="str">
-        <v>s3_round_3_rank_2_seal_id</v>
+        <v>s3_screen_2_rank_2_title</v>
       </c>
       <c r="DL1" t="str">
-        <v>s3_round_3_rank_2_title</v>
+        <v>s3_screen_2_rank_2_subtitle</v>
       </c>
       <c r="DM1" t="str">
-        <v>s3_round_3_rank_2_price_brl</v>
+        <v>s3_screen_2_rank_2_price_brl</v>
       </c>
       <c r="DN1" t="str">
-        <v>s3_round_3_rank_2_price_increase_percent</v>
+        <v>s3_screen_2_rank_2_price_increase_percent</v>
       </c>
       <c r="DO1" t="str">
-        <v>s3_round_3_rank_3_option_id</v>
+        <v>s3_screen_2_rank_3_option_id</v>
       </c>
       <c r="DP1" t="str">
-        <v>s3_round_3_rank_3_cut_id</v>
+        <v>s3_screen_2_rank_3_seal_id</v>
       </c>
       <c r="DQ1" t="str">
-        <v>s3_round_3_rank_3_seal_id</v>
+        <v>s3_screen_2_rank_3_title</v>
       </c>
       <c r="DR1" t="str">
-        <v>s3_round_3_rank_3_title</v>
+        <v>s3_screen_2_rank_3_subtitle</v>
       </c>
       <c r="DS1" t="str">
-        <v>s3_round_3_rank_3_price_brl</v>
+        <v>s3_screen_2_rank_3_price_brl</v>
       </c>
       <c r="DT1" t="str">
-        <v>s3_round_3_rank_3_price_increase_percent</v>
+        <v>s3_screen_2_rank_3_price_increase_percent</v>
       </c>
       <c r="DU1" t="str">
-        <v>s3_timestamp</v>
+        <v>s3_screen_3_rank_1_option_id</v>
       </c>
       <c r="DV1" t="str">
-        <v>full_survey_saved_at</v>
+        <v>s3_screen_3_rank_1_seal_id</v>
+      </c>
+      <c r="DW1" t="str">
+        <v>s3_screen_3_rank_1_title</v>
+      </c>
+      <c r="DX1" t="str">
+        <v>s3_screen_3_rank_1_subtitle</v>
+      </c>
+      <c r="DY1" t="str">
+        <v>s3_screen_3_rank_1_price_brl</v>
+      </c>
+      <c r="DZ1" t="str">
+        <v>s3_screen_3_rank_1_price_increase_percent</v>
+      </c>
+      <c r="EA1" t="str">
+        <v>s3_screen_3_rank_2_option_id</v>
+      </c>
+      <c r="EB1" t="str">
+        <v>s3_screen_3_rank_2_seal_id</v>
+      </c>
+      <c r="EC1" t="str">
+        <v>s3_screen_3_rank_2_title</v>
+      </c>
+      <c r="ED1" t="str">
+        <v>s3_screen_3_rank_2_subtitle</v>
+      </c>
+      <c r="EE1" t="str">
+        <v>s3_screen_3_rank_2_price_brl</v>
+      </c>
+      <c r="EF1" t="str">
+        <v>s3_screen_3_rank_2_price_increase_percent</v>
+      </c>
+      <c r="EG1" t="str">
+        <v>s3_screen_3_rank_3_option_id</v>
+      </c>
+      <c r="EH1" t="str">
+        <v>s3_screen_3_rank_3_seal_id</v>
+      </c>
+      <c r="EI1" t="str">
+        <v>s3_screen_3_rank_3_title</v>
+      </c>
+      <c r="EJ1" t="str">
+        <v>s3_screen_3_rank_3_subtitle</v>
+      </c>
+      <c r="EK1" t="str">
+        <v>s3_screen_3_rank_3_price_brl</v>
+      </c>
+      <c r="EL1" t="str">
+        <v>s3_screen_3_rank_3_price_increase_percent</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PUCPR-1780499543579-LCPIXH</v>
+        <v>UFBA-1778003906957-FUBZE6</v>
       </c>
       <c r="B2" t="str">
-        <v>PUCPR</v>
+        <v>UFBA</v>
       </c>
       <c r="C2" t="str">
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="D2" t="str">
         <v>18–24 years old</v>
       </c>
       <c r="E2" t="str">
-        <v>No schooling or incomplete elementary education</v>
+        <v>Completed high school or incomplete higher education</v>
       </c>
       <c r="F2" t="str">
-        <v>Up to 1 minimum wage — up to R$ 1,621</v>
+        <v>From 2 to 5 minimum wages — R$ 3,242 to R$ 8,105</v>
       </c>
       <c r="G2" t="str">
         <v>Yes</v>
@@ -817,70 +865,70 @@
         <v>Choice experiment / Best-Worst Scaling ranking</v>
       </c>
       <c r="M2" t="str">
-        <v>PUCPR-1780499543579-LCPIXH-session-1</v>
+        <v>UFBA-1778003906957-FUBZE6-session-1</v>
       </c>
       <c r="N2" t="str">
-        <v>session-1-option-2</v>
+        <v>option-3</v>
       </c>
       <c r="O2" t="str">
-        <v>pucpr-cut-2</v>
+        <v>cut-3</v>
       </c>
       <c r="P2" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="R2" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="S2" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="T2" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="V2" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="W2" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="X2" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AF2" t="str">
         <v>red-2</v>
       </c>
-      <c r="Q2" t="str">
-        <v>Beef Option 2 - Red Seal 2</v>
-      </c>
-      <c r="R2" t="str">
-        <v>session-1-option-1</v>
-      </c>
-      <c r="S2" t="str">
-        <v>pucpr-cut-1</v>
-      </c>
-      <c r="T2" t="str">
-        <v>red-1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>Beef Option 1 - Red Seal 1</v>
-      </c>
-      <c r="V2" t="str">
-        <v>session-1-option-4</v>
-      </c>
-      <c r="W2" t="str">
-        <v>pucpr-cut-4</v>
-      </c>
-      <c r="X2" t="str">
-        <v>red-4</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>Beef Option 4 - Red Seal 4</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>session-1-option-5</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>pucpr-cut-5</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>red-5</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>Beef Option 5 - Red Seal 5</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>session-1-option-3</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>pucpr-cut-3</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>red-3</v>
-      </c>
       <c r="AG2" t="str">
-        <v>Beef Option 3 - Red Seal 3</v>
+        <v>Picanha Bovina</v>
       </c>
       <c r="AH2" t="str">
-        <v>2026-06-03T15:12:33.008Z</v>
+        <v>2026-05-05T17:58:35.754Z</v>
       </c>
       <c r="AI2">
         <v>2</v>
@@ -889,7 +937,7 @@
         <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
       </c>
       <c r="AK2" t="str">
-        <v>PUCPR-1780499543579-LCPIXH-session-2</v>
+        <v>UFBA-1778003906957-FUBZE6-session-2</v>
       </c>
       <c r="AL2" t="str">
         <v>Yes</v>
@@ -901,267 +949,3150 @@
         <v>Yes</v>
       </c>
       <c r="AO2" t="str">
-        <v>session-2-option-2</v>
+        <v>session-2-option-3</v>
       </c>
       <c r="AP2" t="str">
-        <v>pucpr-cut-2</v>
+        <v>cut-3</v>
       </c>
       <c r="AQ2" t="str">
-        <v>red-2</v>
+        <v>green-1</v>
       </c>
       <c r="AR2" t="str">
-        <v>Beef Option 2 - Red Seal 2</v>
+        <v>Picanha Bovina</v>
       </c>
       <c r="AS2" t="str">
         <v>session-2-option-4</v>
       </c>
       <c r="AT2" t="str">
-        <v>pucpr-cut-4</v>
+        <v>cut-4</v>
       </c>
       <c r="AU2" t="str">
-        <v>red-4</v>
+        <v>green-2</v>
       </c>
       <c r="AV2" t="str">
-        <v>Beef Option 4 - Red Seal 4</v>
+        <v>Picanha Bovina</v>
       </c>
       <c r="AW2" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="AX2" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="AY2" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="AZ2" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="BA2" t="str">
         <v>session-2-option-1</v>
       </c>
-      <c r="AX2" t="str">
-        <v>pucpr-cut-1</v>
-      </c>
-      <c r="AY2" t="str">
+      <c r="BB2" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="BC2" t="str">
         <v>red-1</v>
       </c>
-      <c r="AZ2" t="str">
-        <v>Beef Option 1 - Red Seal 1</v>
-      </c>
-      <c r="BA2" t="str">
-        <v>session-2-option-3</v>
-      </c>
-      <c r="BB2" t="str">
-        <v>pucpr-cut-3</v>
-      </c>
-      <c r="BC2" t="str">
-        <v>red-3</v>
-      </c>
       <c r="BD2" t="str">
-        <v>Beef Option 3 - Red Seal 3</v>
+        <v>Picanha Bovina</v>
       </c>
       <c r="BE2" t="str">
-        <v>session-2-option-5</v>
+        <v>session-2-option-2</v>
       </c>
       <c r="BF2" t="str">
-        <v>pucpr-cut-5</v>
+        <v>cut-2</v>
       </c>
       <c r="BG2" t="str">
-        <v>red-5</v>
+        <v>red-2</v>
       </c>
       <c r="BH2" t="str">
-        <v>Beef Option 5 - Red Seal 5</v>
+        <v>Picanha Bovina</v>
       </c>
       <c r="BI2" t="str">
-        <v>2026-06-03T15:12:50.621Z</v>
+        <v>2026-05-05T18:08:16.704Z</v>
       </c>
       <c r="BJ2">
         <v>3</v>
       </c>
       <c r="BK2" t="str">
-        <v>3 seals x 3 rotating prices price experiment</v>
+        <v>3 cuts x 3 prices price experiment</v>
       </c>
       <c r="BL2">
         <v>80</v>
       </c>
-      <c r="BM2">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="BN2">
-        <v>0.6666666666666666</v>
+      <c r="BM2" t="str">
+        <v>UFBA-1778003906957-FUBZE6-session-3</v>
+      </c>
+      <c r="BN2" t="str">
+        <v>green-1</v>
       </c>
       <c r="BO2" t="str">
-        <v>PUCPR-1780499543579-LCPIXH-session-3</v>
+        <v>green-2</v>
       </c>
       <c r="BP2" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BQ2" t="str">
+        <v>session-3-green-3-20</v>
+      </c>
+      <c r="BR2" t="str">
+        <v>price-cut-3</v>
+      </c>
+      <c r="BS2" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BT2" t="str">
+        <v>Carne Cultivada - R$ 96,00/kg</v>
+      </c>
+      <c r="BU2">
+        <v>96</v>
+      </c>
+      <c r="BV2">
+        <v>20</v>
+      </c>
+      <c r="BW2" t="str">
+        <v>session-3-green-2-10</v>
+      </c>
+      <c r="BX2" t="str">
+        <v>price-cut-2</v>
+      </c>
+      <c r="BY2" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BZ2" t="str">
+        <v>Orgânica - R$ 88,00/kg</v>
+      </c>
+      <c r="CA2">
+        <v>88</v>
+      </c>
+      <c r="CB2">
+        <v>10</v>
+      </c>
+      <c r="CC2" t="str">
+        <v>session-3-green-1-5</v>
+      </c>
+      <c r="CD2" t="str">
+        <v>price-cut-1</v>
+      </c>
+      <c r="CE2" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CF2" t="str">
+        <v>Carne Bovina - R$ 84,00/kg</v>
+      </c>
+      <c r="CG2">
+        <v>84</v>
+      </c>
+      <c r="CH2">
+        <v>5</v>
+      </c>
+      <c r="CI2" t="str">
+        <v>2026-05-05T18:13:10.577Z</v>
+      </c>
+      <c r="CJ2" t="str">
+        <v>2026-05-05T18:13:11.693Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PUCPR-1778007195721-9L6KSZ</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PUCPR</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Masculino</v>
+      </c>
+      <c r="D3" t="str">
+        <v>60 anos ou mais</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Ensino médio completo ou ensino superior incompleto</v>
+      </c>
+      <c r="F3" t="str">
+        <v>De 2 a 5 salários mínimos — R$ 3.242 a R$ 8.105</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M3" t="str">
+        <v>PUCPR-1778007195721-9L6KSZ-session-1</v>
+      </c>
+      <c r="N3" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="O3" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="P3" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="R3" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="S3" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="T3" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="V3" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="W3" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="X3" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AB3" t="str">
         <v>red-2</v>
       </c>
-      <c r="BQ2" t="str">
+      <c r="AC3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>2026-05-05T18:53:42.368Z</v>
+      </c>
+      <c r="AI3">
+        <v>2</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK3" t="str">
+        <v>PUCPR-1778007195721-9L6KSZ-session-2</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM3">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO3" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AP3" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AQ3" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AR3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AS3" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="AT3" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="AU3" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="AV3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AW3" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="AX3" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AY3" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AZ3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="BA3" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="BB3" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="BC3" t="str">
         <v>red-1</v>
       </c>
-      <c r="BR2" t="str">
-        <v>red-4</v>
-      </c>
-      <c r="BS2" t="str">
-        <v>session-3-round-1-red-1-10</v>
-      </c>
-      <c r="BT2" t="str">
+      <c r="BD3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="BE3" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="BF3" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="BG3" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BH3" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="BI3" t="str">
+        <v>2026-05-05T18:54:41.400Z</v>
+      </c>
+      <c r="BJ3">
+        <v>3</v>
+      </c>
+      <c r="BK3" t="str">
+        <v>3 cuts x 3 prices price experiment</v>
+      </c>
+      <c r="BL3">
+        <v>80</v>
+      </c>
+      <c r="BM3" t="str">
+        <v>PUCPR-1778007195721-9L6KSZ-session-3</v>
+      </c>
+      <c r="BN3" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BO3" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BP3" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BQ3" t="str">
+        <v>session-3-green-2-20</v>
+      </c>
+      <c r="BR3" t="str">
+        <v>price-cut-3</v>
+      </c>
+      <c r="BS3" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BT3" t="str">
+        <v>Carne Cultivada - R$ 96,00/kg</v>
+      </c>
+      <c r="BU3">
+        <v>96</v>
+      </c>
+      <c r="BV3">
+        <v>20</v>
+      </c>
+      <c r="BW3" t="str">
+        <v>session-3-green-1-10</v>
+      </c>
+      <c r="BX3" t="str">
         <v>price-cut-2</v>
       </c>
-      <c r="BU2" t="str">
+      <c r="BY3" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BZ3" t="str">
+        <v>Carne Bovina - R$ 88,00/kg</v>
+      </c>
+      <c r="CA3">
+        <v>88</v>
+      </c>
+      <c r="CB3">
+        <v>10</v>
+      </c>
+      <c r="CC3" t="str">
+        <v>session-3-green-3-5</v>
+      </c>
+      <c r="CD3" t="str">
+        <v>price-cut-1</v>
+      </c>
+      <c r="CE3" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="CF3" t="str">
+        <v>Ôrganica - R$ 84,00/kg</v>
+      </c>
+      <c r="CG3">
+        <v>84</v>
+      </c>
+      <c r="CH3">
+        <v>5</v>
+      </c>
+      <c r="CI3" t="str">
+        <v>2026-05-05T18:56:11.445Z</v>
+      </c>
+      <c r="CJ3" t="str">
+        <v>2026-05-05T18:56:11.639Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PUCPR-1778007438025-GQZBOK</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PUCPR</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Masculino</v>
+      </c>
+      <c r="D4" t="str">
+        <v>45–59 anos</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Ensino médio completo ou ensino superior incompleto</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Até 1 salário mínimo — até R$ 1.621</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M4" t="str">
+        <v>PUCPR-1778007438025-GQZBOK-session-1</v>
+      </c>
+      <c r="N4" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="O4" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="P4" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="R4" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="S4" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="T4" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="V4" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="W4" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="X4" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="AF4" t="str">
         <v>red-1</v>
       </c>
-      <c r="BV2" t="str">
-        <v>Red Seal 1 - R$ 88,00/kg</v>
-      </c>
-      <c r="BW2">
+      <c r="AG4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>2026-05-05T18:57:36.878Z</v>
+      </c>
+      <c r="AI4">
+        <v>2</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK4" t="str">
+        <v>PUCPR-1778007438025-GQZBOK-session-2</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM4">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO4" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="AP4" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AQ4" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AR4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AS4" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AT4" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AU4" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AV4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="AW4" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="AX4" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="AY4" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="AZ4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="BA4" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="BB4" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="BC4" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BD4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="BE4" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="BF4" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="BG4" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BH4" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="BI4" t="str">
+        <v>2026-05-05T18:58:03.129Z</v>
+      </c>
+      <c r="BJ4">
+        <v>3</v>
+      </c>
+      <c r="BK4" t="str">
+        <v>3 cuts x 3 prices price experiment</v>
+      </c>
+      <c r="BL4">
+        <v>80</v>
+      </c>
+      <c r="BM4" t="str">
+        <v>PUCPR-1778007438025-GQZBOK-session-3</v>
+      </c>
+      <c r="BN4" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BO4" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="BP4" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BQ4" t="str">
+        <v>session-3-green-2-5</v>
+      </c>
+      <c r="BR4" t="str">
+        <v>price-cut-1</v>
+      </c>
+      <c r="BS4" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BT4" t="str">
+        <v>Carne Cultivada - R$ 84,00/kg</v>
+      </c>
+      <c r="BU4">
+        <v>84</v>
+      </c>
+      <c r="BV4">
+        <v>5</v>
+      </c>
+      <c r="BW4" t="str">
+        <v>session-3-green-3-20</v>
+      </c>
+      <c r="BX4" t="str">
+        <v>price-cut-3</v>
+      </c>
+      <c r="BY4" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BZ4" t="str">
+        <v>Ôrganica - R$ 96,00/kg</v>
+      </c>
+      <c r="CA4">
+        <v>96</v>
+      </c>
+      <c r="CB4">
+        <v>20</v>
+      </c>
+      <c r="CC4" t="str">
+        <v>session-3-red-2-10</v>
+      </c>
+      <c r="CD4" t="str">
+        <v>price-cut-2</v>
+      </c>
+      <c r="CE4" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="CF4" t="str">
+        <v>Certificação Bem-Estar Animal - R$ 88,00/kg</v>
+      </c>
+      <c r="CG4">
         <v>88</v>
       </c>
-      <c r="BX2">
+      <c r="CH4">
         <v>10</v>
       </c>
-      <c r="BY2" t="str">
-        <v>session-3-round-1-red-4-5</v>
-      </c>
-      <c r="BZ2" t="str">
-        <v>price-cut-3</v>
-      </c>
-      <c r="CA2" t="str">
-        <v>red-4</v>
-      </c>
-      <c r="CB2" t="str">
-        <v>Red Seal 4 - R$ 84,00/kg</v>
-      </c>
-      <c r="CC2">
+      <c r="CI4" t="str">
+        <v>2026-05-05T18:58:22.691Z</v>
+      </c>
+      <c r="CJ4" t="str">
+        <v>2026-05-05T18:58:22.749Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PUCPR-1778505452884-FIXIQ5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PUCPR</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Feminino</v>
+      </c>
+      <c r="D5" t="str">
+        <v>45–59 anos</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Pós-graduação, mestrado ou doutorado</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Até 1 salário mínimo — até R$ 1.621</v>
+      </c>
+      <c r="G5" t="str">
+        <v>No</v>
+      </c>
+      <c r="H5" t="str">
+        <v>No</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>3</v>
+      </c>
+      <c r="BK5" t="str">
+        <v>3 cuts x 3 prices price experiment with 3 screens</v>
+      </c>
+      <c r="BL5">
+        <v>80</v>
+      </c>
+      <c r="BM5" t="str">
+        <v>PUCPR-1778505452884-FIXIQ5-session-3</v>
+      </c>
+      <c r="BN5" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BO5" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="BP5" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CI5" t="str">
+        <v>2026-05-11T14:21:05.550Z</v>
+      </c>
+      <c r="CJ5" t="str">
+        <v>2026-05-11T14:21:05.600Z</v>
+      </c>
+      <c r="CK5" t="str">
+        <v>session-3-s1-green-1-5</v>
+      </c>
+      <c r="CL5" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CM5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="CN5" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CO5">
         <v>84</v>
       </c>
-      <c r="CD2">
+      <c r="CP5">
         <v>5</v>
       </c>
-      <c r="CE2" t="str">
-        <v>session-3-round-1-red-2-20</v>
-      </c>
-      <c r="CF2" t="str">
-        <v>price-cut-1</v>
-      </c>
-      <c r="CG2" t="str">
+      <c r="CQ5" t="str">
+        <v>session-3-s1-red-2-10</v>
+      </c>
+      <c r="CR5" t="str">
         <v>red-2</v>
       </c>
-      <c r="CH2" t="str">
-        <v>Red Seal 2 - R$ 96,00/kg</v>
-      </c>
-      <c r="CI2">
+      <c r="CS5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="CT5" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="CU5">
+        <v>88</v>
+      </c>
+      <c r="CV5">
+        <v>10</v>
+      </c>
+      <c r="CW5" t="str">
+        <v>session-3-s1-red-1-20</v>
+      </c>
+      <c r="CX5" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="CY5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="CZ5" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DA5">
         <v>96</v>
       </c>
-      <c r="CJ2">
+      <c r="DB5">
         <v>20</v>
       </c>
-      <c r="CK2" t="str">
-        <v>session-3-round-2-red-2-5</v>
-      </c>
-      <c r="CL2" t="str">
-        <v>price-cut-1</v>
-      </c>
-      <c r="CM2" t="str">
+      <c r="DC5" t="str">
+        <v>session-3-s3-red-1-5</v>
+      </c>
+      <c r="DD5" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="DE5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="DF5" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DG5">
+        <v>84</v>
+      </c>
+      <c r="DH5">
+        <v>5</v>
+      </c>
+      <c r="DI5" t="str">
+        <v>session-3-s3-green-1-10</v>
+      </c>
+      <c r="DJ5" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="DK5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="DL5" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DM5">
+        <v>88</v>
+      </c>
+      <c r="DN5">
+        <v>10</v>
+      </c>
+      <c r="DO5" t="str">
+        <v>session-3-s3-red-2-20</v>
+      </c>
+      <c r="DP5" t="str">
         <v>red-2</v>
       </c>
-      <c r="CN2" t="str">
-        <v>Red Seal 2 - R$ 84,00/kg</v>
-      </c>
-      <c r="CO2">
+      <c r="DQ5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="DR5" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="DS5">
+        <v>96</v>
+      </c>
+      <c r="DT5">
+        <v>20</v>
+      </c>
+      <c r="DU5" t="str">
+        <v>session-3-s2-green-1-20</v>
+      </c>
+      <c r="DV5" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="DW5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="DX5" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DY5">
+        <v>96</v>
+      </c>
+      <c r="DZ5">
+        <v>20</v>
+      </c>
+      <c r="EA5" t="str">
+        <v>session-3-s2-red-1-10</v>
+      </c>
+      <c r="EB5" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="EC5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="ED5" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="EE5">
+        <v>88</v>
+      </c>
+      <c r="EF5">
+        <v>10</v>
+      </c>
+      <c r="EG5" t="str">
+        <v>session-3-s2-red-2-5</v>
+      </c>
+      <c r="EH5" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="EI5" t="str">
+        <v>Picanha Fatiada</v>
+      </c>
+      <c r="EJ5" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="EK5">
         <v>84</v>
       </c>
-      <c r="CP2">
+      <c r="EL5">
         <v>5</v>
       </c>
-      <c r="CQ2" t="str">
-        <v>session-3-round-2-red-4-10</v>
-      </c>
-      <c r="CR2" t="str">
-        <v>price-cut-3</v>
-      </c>
-      <c r="CS2" t="str">
-        <v>red-4</v>
-      </c>
-      <c r="CT2" t="str">
-        <v>Red Seal 4 - R$ 88,00/kg</v>
-      </c>
-      <c r="CU2">
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>UFBA-1778509527824-BOWPK4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>UFBA</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Prefiro não informar</v>
+      </c>
+      <c r="D6" t="str">
+        <v>60 anos ou mais</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Pós-graduação, mestrado ou doutorado</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Até 1 salário mínimo — até R$ 1.621</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M6" t="str">
+        <v>UFBA-1778509527824-BOWPK4-session-1</v>
+      </c>
+      <c r="N6" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="O6" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="P6" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="R6" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="S6" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="T6" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="U6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="V6" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="W6" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="X6" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AG6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="AH6" t="str">
+        <v>2026-05-11T14:26:50.214Z</v>
+      </c>
+      <c r="AI6">
+        <v>2</v>
+      </c>
+      <c r="AJ6" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK6" t="str">
+        <v>UFBA-1778509527824-BOWPK4-session-2</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM6">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO6" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="AP6" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="AQ6" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="AR6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="AS6" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="AT6" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AU6" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AV6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="AW6" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AX6" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AY6" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AZ6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="BA6" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="BB6" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="BC6" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BD6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="BE6" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="BF6" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="BG6" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BH6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="BI6" t="str">
+        <v>2026-05-11T14:27:16.628Z</v>
+      </c>
+      <c r="BJ6">
+        <v>3</v>
+      </c>
+      <c r="BK6" t="str">
+        <v>3 cuts x 3 prices price experiment with 3 screens</v>
+      </c>
+      <c r="BL6">
+        <v>80</v>
+      </c>
+      <c r="BM6" t="str">
+        <v>UFBA-1778509527824-BOWPK4-session-3</v>
+      </c>
+      <c r="BN6" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BO6" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="BP6" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="CI6" t="str">
+        <v>2026-05-11T14:32:24.495Z</v>
+      </c>
+      <c r="CJ6" t="str">
+        <v>2026-05-11T14:32:24.674Z</v>
+      </c>
+      <c r="CK6" t="str">
+        <v>session-3-s3-red-2-20</v>
+      </c>
+      <c r="CL6" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="CM6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="CN6" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="CO6">
+        <v>96</v>
+      </c>
+      <c r="CP6">
+        <v>20</v>
+      </c>
+      <c r="CQ6" t="str">
+        <v>session-3-s3-red-1-10</v>
+      </c>
+      <c r="CR6" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="CS6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="CT6" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="CU6">
         <v>88</v>
       </c>
-      <c r="CV2">
+      <c r="CV6">
         <v>10</v>
       </c>
-      <c r="CW2" t="str">
-        <v>session-3-round-2-red-1-20</v>
-      </c>
-      <c r="CX2" t="str">
-        <v>price-cut-2</v>
-      </c>
-      <c r="CY2" t="str">
+      <c r="CW6" t="str">
+        <v>session-3-s3-green-1-5</v>
+      </c>
+      <c r="CX6" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CY6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="CZ6" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DA6">
+        <v>84</v>
+      </c>
+      <c r="DB6">
+        <v>5</v>
+      </c>
+      <c r="DC6" t="str">
+        <v>session-3-s2-green-1-10</v>
+      </c>
+      <c r="DD6" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="DE6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="DF6" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DG6">
+        <v>88</v>
+      </c>
+      <c r="DH6">
+        <v>10</v>
+      </c>
+      <c r="DI6" t="str">
+        <v>session-3-s2-red-2-5</v>
+      </c>
+      <c r="DJ6" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="DK6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="DL6" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="DM6">
+        <v>84</v>
+      </c>
+      <c r="DN6">
+        <v>5</v>
+      </c>
+      <c r="DO6" t="str">
+        <v>session-3-s2-red-1-20</v>
+      </c>
+      <c r="DP6" t="str">
         <v>red-1</v>
       </c>
-      <c r="CZ2" t="str">
-        <v>Red Seal 1 - R$ 96,00/kg</v>
-      </c>
-      <c r="DA2">
+      <c r="DQ6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="DR6" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DS6">
         <v>96</v>
       </c>
-      <c r="DB2">
+      <c r="DT6">
         <v>20</v>
       </c>
-      <c r="DC2" t="str">
-        <v>session-3-round-3-red-1-5</v>
-      </c>
-      <c r="DD2" t="str">
-        <v>price-cut-2</v>
-      </c>
-      <c r="DE2" t="str">
+      <c r="DU6" t="str">
+        <v>session-3-s1-red-1-5</v>
+      </c>
+      <c r="DV6" t="str">
         <v>red-1</v>
       </c>
-      <c r="DF2" t="str">
-        <v>Red Seal 1 - R$ 84,00/kg</v>
-      </c>
-      <c r="DG2">
+      <c r="DW6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="DX6" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DY6">
         <v>84</v>
       </c>
-      <c r="DH2">
+      <c r="DZ6">
         <v>5</v>
       </c>
-      <c r="DI2" t="str">
-        <v>session-3-round-3-red-4-20</v>
-      </c>
-      <c r="DJ2" t="str">
-        <v>price-cut-3</v>
-      </c>
-      <c r="DK2" t="str">
-        <v>red-4</v>
-      </c>
-      <c r="DL2" t="str">
-        <v>Red Seal 4 - R$ 96,00/kg</v>
-      </c>
-      <c r="DM2">
+      <c r="EA6" t="str">
+        <v>session-3-s1-green-1-20</v>
+      </c>
+      <c r="EB6" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="EC6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="ED6" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="EE6">
         <v>96</v>
       </c>
-      <c r="DN2">
+      <c r="EF6">
         <v>20</v>
       </c>
-      <c r="DO2" t="str">
-        <v>session-3-round-3-red-2-10</v>
-      </c>
-      <c r="DP2" t="str">
-        <v>price-cut-1</v>
-      </c>
-      <c r="DQ2" t="str">
+      <c r="EG6" t="str">
+        <v>session-3-s1-red-2-10</v>
+      </c>
+      <c r="EH6" t="str">
         <v>red-2</v>
       </c>
-      <c r="DR2" t="str">
-        <v>Red Seal 2 - R$ 88,00/kg</v>
-      </c>
-      <c r="DS2">
+      <c r="EI6" t="str">
+        <v>Picanha Bovina</v>
+      </c>
+      <c r="EJ6" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="EK6">
         <v>88</v>
       </c>
-      <c r="DT2">
+      <c r="EL6">
         <v>10</v>
       </c>
-      <c r="DU2" t="str">
-        <v>2026-06-03T15:13:15.468Z</v>
-      </c>
-      <c r="DV2" t="str">
-        <v>2026-06-03T15:13:15.552Z</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PUCPR-1778679328020-3IWEVM</v>
+      </c>
+      <c r="B7" t="str">
+        <v>PUCPR</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Feminino</v>
+      </c>
+      <c r="D7" t="str">
+        <v>45–59 anos</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Ensino superior completo</v>
+      </c>
+      <c r="F7" t="str">
+        <v>De 5 a 10 salários mínimos — R$ 8.105 a R$ 16.210</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M7" t="str">
+        <v>PUCPR-1778679328020-3IWEVM-session-1</v>
+      </c>
+      <c r="N7" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="O7" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="P7" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="R7" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="S7" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="T7" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="V7" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="W7" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="X7" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AG7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AH7" t="str">
+        <v>2026-05-13T14:02:18.869Z</v>
+      </c>
+      <c r="AI7">
+        <v>2</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK7" t="str">
+        <v>PUCPR-1778679328020-3IWEVM-session-2</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM7">
+        <v>5</v>
+      </c>
+      <c r="AN7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO7" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="AP7" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="AQ7" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="AR7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AS7" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="AT7" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="AU7" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="AV7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AW7" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AX7" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AY7" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AZ7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="BA7" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="BB7" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="BC7" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BD7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="BE7" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="BF7" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="BG7" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="BH7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="BI7" t="str">
+        <v>2026-05-13T15:06:37.312Z</v>
+      </c>
+      <c r="BJ7">
+        <v>3</v>
+      </c>
+      <c r="BK7" t="str">
+        <v>3 cuts x 3 prices price experiment with 3 screens</v>
+      </c>
+      <c r="BL7">
+        <v>80</v>
+      </c>
+      <c r="BM7" t="str">
+        <v>PUCPR-1778679328020-3IWEVM-session-3</v>
+      </c>
+      <c r="BN7" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BO7" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BP7" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="CI7" t="str">
+        <v>2026-05-13T15:17:01.544Z</v>
+      </c>
+      <c r="CJ7" t="str">
+        <v>2026-05-13T15:17:01.806Z</v>
+      </c>
+      <c r="CK7" t="str">
+        <v>session-3-s2-red-1-10</v>
+      </c>
+      <c r="CL7" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="CM7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CN7" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="CO7">
+        <v>88</v>
+      </c>
+      <c r="CP7">
+        <v>10</v>
+      </c>
+      <c r="CQ7" t="str">
+        <v>session-3-s2-green-1-5</v>
+      </c>
+      <c r="CR7" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CS7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CT7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CU7">
+        <v>84</v>
+      </c>
+      <c r="CV7">
+        <v>5</v>
+      </c>
+      <c r="CW7" t="str">
+        <v>session-3-s2-green-2-20</v>
+      </c>
+      <c r="CX7" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="CY7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CZ7" t="str">
+        <v>Carne Cultivada</v>
+      </c>
+      <c r="DA7">
+        <v>96</v>
+      </c>
+      <c r="DB7">
+        <v>20</v>
+      </c>
+      <c r="DC7" t="str">
+        <v>session-3-s1-green-1-10</v>
+      </c>
+      <c r="DD7" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="DE7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DF7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DG7">
+        <v>88</v>
+      </c>
+      <c r="DH7">
+        <v>10</v>
+      </c>
+      <c r="DI7" t="str">
+        <v>session-3-s1-green-2-5</v>
+      </c>
+      <c r="DJ7" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="DK7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DL7" t="str">
+        <v>Carne Cultivada</v>
+      </c>
+      <c r="DM7">
+        <v>84</v>
+      </c>
+      <c r="DN7">
+        <v>5</v>
+      </c>
+      <c r="DO7" t="str">
+        <v>session-3-s1-red-1-20</v>
+      </c>
+      <c r="DP7" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="DQ7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DR7" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DS7">
+        <v>96</v>
+      </c>
+      <c r="DT7">
+        <v>20</v>
+      </c>
+      <c r="DU7" t="str">
+        <v>session-3-s3-green-2-10</v>
+      </c>
+      <c r="DV7" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="DW7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DX7" t="str">
+        <v>Carne Cultivada</v>
+      </c>
+      <c r="DY7">
+        <v>88</v>
+      </c>
+      <c r="DZ7">
+        <v>10</v>
+      </c>
+      <c r="EA7" t="str">
+        <v>session-3-s3-red-1-5</v>
+      </c>
+      <c r="EB7" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="EC7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="ED7" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="EE7">
+        <v>84</v>
+      </c>
+      <c r="EF7">
+        <v>5</v>
+      </c>
+      <c r="EG7" t="str">
+        <v>session-3-s3-green-1-20</v>
+      </c>
+      <c r="EH7" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="EI7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="EJ7" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="EK7">
+        <v>96</v>
+      </c>
+      <c r="EL7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PUCPR-1778685490476-2YT6BE</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PUCPR</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Masculino</v>
+      </c>
+      <c r="D8" t="str">
+        <v>35–44 anos</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Ensino superior completo</v>
+      </c>
+      <c r="F8" t="str">
+        <v>De 2 a 5 salários mínimos — R$ 3.242 a R$ 8.105</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M8" t="str">
+        <v>PUCPR-1778685490476-2YT6BE-session-1</v>
+      </c>
+      <c r="N8" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="O8" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="P8" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="R8" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="S8" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="T8" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="V8" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="W8" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="X8" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="AG8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AH8" t="str">
+        <v>2026-05-13T15:21:44.217Z</v>
+      </c>
+      <c r="AI8">
+        <v>2</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>PUCPR-1778685490476-2YT6BE-session-2</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM8">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO8" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="AP8" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="AQ8" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="AR8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AS8" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AT8" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AU8" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AV8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="AW8" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="AX8" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AY8" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AZ8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="BA8" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="BB8" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="BC8" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BD8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="BE8" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="BF8" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="BG8" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BH8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="BI8" t="str">
+        <v>2026-05-13T15:23:06.178Z</v>
+      </c>
+      <c r="BJ8">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="str">
+        <v>3 cuts x 3 prices price experiment with 3 screens</v>
+      </c>
+      <c r="BL8">
+        <v>80</v>
+      </c>
+      <c r="BM8" t="str">
+        <v>PUCPR-1778685490476-2YT6BE-session-3</v>
+      </c>
+      <c r="BN8" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="BO8" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BP8" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="CI8" t="str">
+        <v>2026-05-13T15:24:04.305Z</v>
+      </c>
+      <c r="CJ8" t="str">
+        <v>2026-05-13T15:24:04.426Z</v>
+      </c>
+      <c r="CK8" t="str">
+        <v>session-3-s2-red-1-10</v>
+      </c>
+      <c r="CL8" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="CM8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CN8" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="CO8">
+        <v>88</v>
+      </c>
+      <c r="CP8">
+        <v>10</v>
+      </c>
+      <c r="CQ8" t="str">
+        <v>session-3-s2-green-1-20</v>
+      </c>
+      <c r="CR8" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CS8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CT8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CU8">
+        <v>96</v>
+      </c>
+      <c r="CV8">
+        <v>20</v>
+      </c>
+      <c r="CW8" t="str">
+        <v>session-3-s2-red-2-5</v>
+      </c>
+      <c r="CX8" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="CY8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="CZ8" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="DA8">
+        <v>84</v>
+      </c>
+      <c r="DB8">
+        <v>5</v>
+      </c>
+      <c r="DC8" t="str">
+        <v>session-3-s2-green-1-5</v>
+      </c>
+      <c r="DD8" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="DE8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DF8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DG8">
+        <v>84</v>
+      </c>
+      <c r="DH8">
+        <v>5</v>
+      </c>
+      <c r="DI8" t="str">
+        <v>session-3-s2-red-2-10</v>
+      </c>
+      <c r="DJ8" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="DK8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DL8" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="DM8">
+        <v>88</v>
+      </c>
+      <c r="DN8">
+        <v>10</v>
+      </c>
+      <c r="DO8" t="str">
+        <v>session-3-s2-green-2-20</v>
+      </c>
+      <c r="DP8" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="DQ8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DR8" t="str">
+        <v>Carne Cultivada</v>
+      </c>
+      <c r="DS8">
+        <v>96</v>
+      </c>
+      <c r="DT8">
+        <v>20</v>
+      </c>
+      <c r="DU8" t="str">
+        <v>session-3-s3-red-2-5</v>
+      </c>
+      <c r="DV8" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="DW8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="DX8" t="str">
+        <v>Bem-Estar Animal</v>
+      </c>
+      <c r="DY8">
+        <v>84</v>
+      </c>
+      <c r="DZ8">
+        <v>5</v>
+      </c>
+      <c r="EA8" t="str">
+        <v>session-3-s3-green-1-20</v>
+      </c>
+      <c r="EB8" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="EC8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="ED8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="EE8">
+        <v>96</v>
+      </c>
+      <c r="EF8">
+        <v>20</v>
+      </c>
+      <c r="EG8" t="str">
+        <v>session-3-s3-green-2-10</v>
+      </c>
+      <c r="EH8" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="EI8" t="str">
+        <v>Carne Bovina</v>
+      </c>
+      <c r="EJ8" t="str">
+        <v>Carne Cultivada</v>
+      </c>
+      <c r="EK8">
+        <v>88</v>
+      </c>
+      <c r="EL8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PUCPR-1779276609319-Z398XS</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PUCPR</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Feminino</v>
+      </c>
+      <c r="D9" t="str">
+        <v>60 anos ou mais</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Pós-graduação, mestrado ou doutorado</v>
+      </c>
+      <c r="F9" t="str">
+        <v>De 2 a 5 salários mínimos — R$ 3.242 a R$ 8.105</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M9" t="str">
+        <v>PUCPR-1779276609319-Z398XS-session-1</v>
+      </c>
+      <c r="N9" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="O9" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="P9" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="R9" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="S9" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="T9" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="U9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="V9" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="W9" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="X9" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AG9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AH9" t="str">
+        <v>2026-05-20T11:30:23.734Z</v>
+      </c>
+      <c r="AI9">
+        <v>2</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK9" t="str">
+        <v>PUCPR-1779276609319-Z398XS-session-2</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM9">
+        <v>5</v>
+      </c>
+      <c r="AN9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO9" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="AP9" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AQ9" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AR9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AS9" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="AT9" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="AU9" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="AV9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AW9" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AX9" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AY9" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AZ9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BA9" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="BB9" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="BC9" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BD9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BE9" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="BF9" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="BG9" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BH9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BI9" t="str">
+        <v>2026-05-20T11:31:12.313Z</v>
+      </c>
+      <c r="BJ9">
+        <v>3</v>
+      </c>
+      <c r="BK9" t="str">
+        <v>3 cuts x 3 prices price experiment with 3 screens</v>
+      </c>
+      <c r="BL9">
+        <v>80</v>
+      </c>
+      <c r="BM9" t="str">
+        <v>PUCPR-1779276609319-Z398XS-session-3</v>
+      </c>
+      <c r="BN9" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BO9" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="BP9" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="CI9" t="str">
+        <v>2026-05-20T11:39:32.172Z</v>
+      </c>
+      <c r="CJ9" t="str">
+        <v>2026-05-20T11:39:32.433Z</v>
+      </c>
+      <c r="CK9" t="str">
+        <v>session-3-s1-red-2-10</v>
+      </c>
+      <c r="CL9" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="CM9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CN9" t="str">
+        <v>Bem-estar animal</v>
+      </c>
+      <c r="CO9">
+        <v>88</v>
+      </c>
+      <c r="CP9">
+        <v>10</v>
+      </c>
+      <c r="CQ9" t="str">
+        <v>session-3-s1-green-3-5</v>
+      </c>
+      <c r="CR9" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="CS9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CT9" t="str">
+        <v>Orgânica</v>
+      </c>
+      <c r="CU9">
+        <v>84</v>
+      </c>
+      <c r="CV9">
+        <v>5</v>
+      </c>
+      <c r="CW9" t="str">
+        <v>session-3-s1-green-2-20</v>
+      </c>
+      <c r="CX9" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="CY9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CZ9" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="DA9">
+        <v>96</v>
+      </c>
+      <c r="DB9">
+        <v>20</v>
+      </c>
+      <c r="DC9" t="str">
+        <v>session-3-s3-green-2-5</v>
+      </c>
+      <c r="DD9" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="DE9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DF9" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="DG9">
+        <v>84</v>
+      </c>
+      <c r="DH9">
+        <v>5</v>
+      </c>
+      <c r="DI9" t="str">
+        <v>session-3-s3-red-2-20</v>
+      </c>
+      <c r="DJ9" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="DK9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DL9" t="str">
+        <v>Bem-estar animal</v>
+      </c>
+      <c r="DM9">
+        <v>96</v>
+      </c>
+      <c r="DN9">
+        <v>20</v>
+      </c>
+      <c r="DO9" t="str">
+        <v>session-3-s3-green-3-10</v>
+      </c>
+      <c r="DP9" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="DQ9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DR9" t="str">
+        <v>Orgânica</v>
+      </c>
+      <c r="DS9">
+        <v>88</v>
+      </c>
+      <c r="DT9">
+        <v>10</v>
+      </c>
+      <c r="DU9" t="str">
+        <v>session-3-s2-green-3-20</v>
+      </c>
+      <c r="DV9" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="DW9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DX9" t="str">
+        <v>Orgânica</v>
+      </c>
+      <c r="DY9">
+        <v>96</v>
+      </c>
+      <c r="DZ9">
+        <v>20</v>
+      </c>
+      <c r="EA9" t="str">
+        <v>session-3-s2-green-2-10</v>
+      </c>
+      <c r="EB9" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="EC9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="ED9" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="EE9">
+        <v>88</v>
+      </c>
+      <c r="EF9">
+        <v>10</v>
+      </c>
+      <c r="EG9" t="str">
+        <v>session-3-s2-red-2-5</v>
+      </c>
+      <c r="EH9" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="EI9" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="EJ9" t="str">
+        <v>Bem-estar animal</v>
+      </c>
+      <c r="EK9">
+        <v>84</v>
+      </c>
+      <c r="EL9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PUCPR-1779278166795-D1OORX</v>
+      </c>
+      <c r="B10" t="str">
+        <v>PUCPR</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Masculino</v>
+      </c>
+      <c r="D10" t="str">
+        <v>18–24 anos</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Sem escolaridade ou ensino fundamental incompleto</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Até 1 salário mínimo — até R$ 1.621</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M10" t="str">
+        <v>PUCPR-1779278166795-D1OORX-session-1</v>
+      </c>
+      <c r="N10" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="O10" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="P10" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="R10" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="S10" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="T10" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="U10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="V10" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="W10" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="X10" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AG10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AH10" t="str">
+        <v>2026-05-20T11:58:46.485Z</v>
+      </c>
+      <c r="AI10">
+        <v>2</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK10" t="str">
+        <v>PUCPR-1779278166795-D1OORX-session-2</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM10">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO10" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AP10" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AQ10" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AR10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AS10" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="AT10" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="AU10" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="AV10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AW10" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="AX10" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AY10" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AZ10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BA10" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="BB10" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="BC10" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BD10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BE10" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="BF10" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="BG10" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="BH10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BI10" t="str">
+        <v>2026-05-20T12:03:36.487Z</v>
+      </c>
+      <c r="BJ10">
+        <v>3</v>
+      </c>
+      <c r="BK10" t="str">
+        <v>3 cuts x 3 prices price experiment with 3 screens</v>
+      </c>
+      <c r="BL10">
+        <v>80</v>
+      </c>
+      <c r="BM10" t="str">
+        <v>PUCPR-1779278166795-D1OORX-session-3</v>
+      </c>
+      <c r="BN10" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BO10" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BP10" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CI10" t="str">
+        <v>2026-05-20T12:04:22.739Z</v>
+      </c>
+      <c r="CJ10" t="str">
+        <v>2026-05-20T12:04:23.088Z</v>
+      </c>
+      <c r="CK10" t="str">
+        <v>session-3-s1-red-1-20</v>
+      </c>
+      <c r="CL10" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="CM10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CN10" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="CO10">
+        <v>96</v>
+      </c>
+      <c r="CP10">
+        <v>20</v>
+      </c>
+      <c r="CQ10" t="str">
+        <v>session-3-s1-green-1-5</v>
+      </c>
+      <c r="CR10" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="CS10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CT10" t="str">
+        <v>Tradicional</v>
+      </c>
+      <c r="CU10">
+        <v>84</v>
+      </c>
+      <c r="CV10">
+        <v>5</v>
+      </c>
+      <c r="CW10" t="str">
+        <v>session-3-s1-green-2-10</v>
+      </c>
+      <c r="CX10" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="CY10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CZ10" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="DA10">
+        <v>88</v>
+      </c>
+      <c r="DB10">
+        <v>10</v>
+      </c>
+      <c r="DC10" t="str">
+        <v>session-3-s2-green-2-5</v>
+      </c>
+      <c r="DD10" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="DE10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DF10" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="DG10">
+        <v>84</v>
+      </c>
+      <c r="DH10">
+        <v>5</v>
+      </c>
+      <c r="DI10" t="str">
+        <v>session-3-s2-red-1-10</v>
+      </c>
+      <c r="DJ10" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="DK10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DL10" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DM10">
+        <v>88</v>
+      </c>
+      <c r="DN10">
+        <v>10</v>
+      </c>
+      <c r="DO10" t="str">
+        <v>session-3-s2-green-1-20</v>
+      </c>
+      <c r="DP10" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="DQ10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DR10" t="str">
+        <v>Tradicional</v>
+      </c>
+      <c r="DS10">
+        <v>96</v>
+      </c>
+      <c r="DT10">
+        <v>20</v>
+      </c>
+      <c r="DU10" t="str">
+        <v>session-3-s3-red-1-5</v>
+      </c>
+      <c r="DV10" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="DW10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DX10" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DY10">
+        <v>84</v>
+      </c>
+      <c r="DZ10">
+        <v>5</v>
+      </c>
+      <c r="EA10" t="str">
+        <v>session-3-s3-green-2-20</v>
+      </c>
+      <c r="EB10" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="EC10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="ED10" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="EE10">
+        <v>96</v>
+      </c>
+      <c r="EF10">
+        <v>20</v>
+      </c>
+      <c r="EG10" t="str">
+        <v>session-3-s3-green-1-10</v>
+      </c>
+      <c r="EH10" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="EI10" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="EJ10" t="str">
+        <v>Tradicional</v>
+      </c>
+      <c r="EK10">
+        <v>88</v>
+      </c>
+      <c r="EL10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>UFBA-1779278884534-QK0Z8T</v>
+      </c>
+      <c r="B11" t="str">
+        <v>UFBA</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Masculino</v>
+      </c>
+      <c r="D11" t="str">
+        <v>60 anos ou mais</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Pós-graduação, mestrado ou doutorado</v>
+      </c>
+      <c r="F11" t="str">
+        <v>De 1 a 2 salários mínimos — R$ 1.621 a R$ 3.242</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="M11" t="str">
+        <v>UFBA-1779278884534-QK0Z8T-session-1</v>
+      </c>
+      <c r="N11" t="str">
+        <v>option-4</v>
+      </c>
+      <c r="O11" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="P11" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="R11" t="str">
+        <v>option-1</v>
+      </c>
+      <c r="S11" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="T11" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="U11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="V11" t="str">
+        <v>option-5</v>
+      </c>
+      <c r="W11" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="X11" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>option-3</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>option-2</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="AG11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AH11" t="str">
+        <v>2026-05-20T12:09:33.558Z</v>
+      </c>
+      <c r="AI11">
+        <v>2</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v>Seal descriptions + Choice experiment / Best-Worst Scaling ranking</v>
+      </c>
+      <c r="AK11" t="str">
+        <v>UFBA-1779278884534-QK0Z8T-session-2</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AM11">
+        <v>5</v>
+      </c>
+      <c r="AN11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AO11" t="str">
+        <v>session-2-option-1</v>
+      </c>
+      <c r="AP11" t="str">
+        <v>cut-1</v>
+      </c>
+      <c r="AQ11" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="AR11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AS11" t="str">
+        <v>session-2-option-4</v>
+      </c>
+      <c r="AT11" t="str">
+        <v>cut-4</v>
+      </c>
+      <c r="AU11" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="AV11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="AW11" t="str">
+        <v>session-2-option-5</v>
+      </c>
+      <c r="AX11" t="str">
+        <v>cut-5</v>
+      </c>
+      <c r="AY11" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="AZ11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BA11" t="str">
+        <v>session-2-option-2</v>
+      </c>
+      <c r="BB11" t="str">
+        <v>cut-2</v>
+      </c>
+      <c r="BC11" t="str">
+        <v>red-2</v>
+      </c>
+      <c r="BD11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BE11" t="str">
+        <v>session-2-option-3</v>
+      </c>
+      <c r="BF11" t="str">
+        <v>cut-3</v>
+      </c>
+      <c r="BG11" t="str">
+        <v>green-1</v>
+      </c>
+      <c r="BH11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="BI11" t="str">
+        <v>2026-05-20T12:10:08.432Z</v>
+      </c>
+      <c r="BJ11">
+        <v>3</v>
+      </c>
+      <c r="BK11" t="str">
+        <v>3 cuts x 3 prices price experiment with 3 screens</v>
+      </c>
+      <c r="BL11">
+        <v>80</v>
+      </c>
+      <c r="BM11" t="str">
+        <v>UFBA-1779278884534-QK0Z8T-session-3</v>
+      </c>
+      <c r="BN11" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="BO11" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="BP11" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="CI11" t="str">
+        <v>2026-05-20T12:10:53.867Z</v>
+      </c>
+      <c r="CJ11" t="str">
+        <v>2026-05-20T12:10:53.947Z</v>
+      </c>
+      <c r="CK11" t="str">
+        <v>session-3-s3-green-3-10</v>
+      </c>
+      <c r="CL11" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="CM11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CN11" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="CO11">
+        <v>88</v>
+      </c>
+      <c r="CP11">
+        <v>10</v>
+      </c>
+      <c r="CQ11" t="str">
+        <v>session-3-s3-red-1-5</v>
+      </c>
+      <c r="CR11" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="CS11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CT11" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="CU11">
+        <v>84</v>
+      </c>
+      <c r="CV11">
+        <v>5</v>
+      </c>
+      <c r="CW11" t="str">
+        <v>session-3-s3-green-2-20</v>
+      </c>
+      <c r="CX11" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="CY11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="CZ11" t="str">
+        <v>Orgânica</v>
+      </c>
+      <c r="DA11">
+        <v>96</v>
+      </c>
+      <c r="DB11">
+        <v>20</v>
+      </c>
+      <c r="DC11" t="str">
+        <v>session-3-s1-green-2-10</v>
+      </c>
+      <c r="DD11" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="DE11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DF11" t="str">
+        <v>Orgânica</v>
+      </c>
+      <c r="DG11">
+        <v>88</v>
+      </c>
+      <c r="DH11">
+        <v>10</v>
+      </c>
+      <c r="DI11" t="str">
+        <v>session-3-s1-green-3-5</v>
+      </c>
+      <c r="DJ11" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="DK11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DL11" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="DM11">
+        <v>84</v>
+      </c>
+      <c r="DN11">
+        <v>5</v>
+      </c>
+      <c r="DO11" t="str">
+        <v>session-3-s1-red-1-20</v>
+      </c>
+      <c r="DP11" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="DQ11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DR11" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DS11">
+        <v>96</v>
+      </c>
+      <c r="DT11">
+        <v>20</v>
+      </c>
+      <c r="DU11" t="str">
+        <v>session-3-s2-red-1-10</v>
+      </c>
+      <c r="DV11" t="str">
+        <v>red-1</v>
+      </c>
+      <c r="DW11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="DX11" t="str">
+        <v>Angus</v>
+      </c>
+      <c r="DY11">
+        <v>88</v>
+      </c>
+      <c r="DZ11">
+        <v>10</v>
+      </c>
+      <c r="EA11" t="str">
+        <v>session-3-s2-green-2-5</v>
+      </c>
+      <c r="EB11" t="str">
+        <v>green-2</v>
+      </c>
+      <c r="EC11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="ED11" t="str">
+        <v>Orgânica</v>
+      </c>
+      <c r="EE11">
+        <v>84</v>
+      </c>
+      <c r="EF11">
+        <v>5</v>
+      </c>
+      <c r="EG11" t="str">
+        <v>session-3-s2-green-3-20</v>
+      </c>
+      <c r="EH11" t="str">
+        <v>green-3</v>
+      </c>
+      <c r="EI11" t="str">
+        <v>Picanha bovina</v>
+      </c>
+      <c r="EJ11" t="str">
+        <v>Cultivada</v>
+      </c>
+      <c r="EK11">
+        <v>96</v>
+      </c>
+      <c r="EL11">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:DV2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:EL11"/>
   </ignoredErrors>
 </worksheet>
 </file>